--- a/M1.xlsx
+++ b/M1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DownTown\Desktop\نتيجة\Result\2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\نتيجة\Result\M1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C6E9B01-1C7B-4150-83E5-089F0EFD1B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691A465B-99DB-4EAF-82EA-1464593A69E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -395,7 +395,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="00000000000000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,6 +451,14 @@
       <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -598,7 +606,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -687,13 +695,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="2"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="20">
     <dxf>
       <font>
         <b/>
@@ -1229,6 +1240,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3221,8 +3239,8 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="18" x14ac:dyDescent="0.3">
-      <c r="A36" s="27">
-        <v>31308281800062</v>
+      <c r="A36" s="30">
+        <v>31309030200607</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>44</v>
@@ -3269,8 +3287,8 @@
       </c>
     </row>
     <row r="37" spans="1:15" ht="18" x14ac:dyDescent="0.3">
-      <c r="A37" s="27">
-        <v>31309030200607</v>
+      <c r="A37" s="30">
+        <v>31308281800062</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>45</v>
@@ -4105,10 +4123,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A56 A30">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="برجاء مراجعة الحسابات">
+      <formula>NOT(ISERROR(SEARCH("برجاء مراجعة الحسابات",B1)))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:A29 A31:A55">
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
